--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -280,12 +280,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$11</f>
+              <f>'欠陥収束'!$A$2:$A$31</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$11</f>
+              <f>'欠陥収束'!$B$2:$B$31</f>
             </numRef>
           </yVal>
         </ser>
@@ -314,12 +314,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$11</f>
+              <f>'欠陥収束'!$A$2:$A$31</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$11</f>
+              <f>'欠陥収束'!$C$2:$C$31</f>
             </numRef>
           </yVal>
         </ser>
@@ -348,12 +348,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$11</f>
+              <f>'欠陥収束'!$A$2:$A$31</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$11</f>
+              <f>'欠陥収束'!$D$2:$D$31</f>
             </numRef>
           </yVal>
         </ser>
@@ -364,7 +364,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46139"/>
+          <max val="46159"/>
           <min val="46130"/>
         </scaling>
         <axPos val="l"/>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1942,18 +1942,94 @@
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
     </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>combined 画像の地理境界外ピークが CSV に混入する</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>タイル座標のフロア演算により combined 画像の端タイルが地理的メッシュ境界より約17px外側へはみ出しており、そのはみ出し部分で検出されたピークが CSV に混入する。9メッシュ解析の検証で analysis_count=2/3 の異常ピーク34件として確認。</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>解析エンジン</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>src/mesh_analyze.c</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>毎回</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>対応完了</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>src/mesh_analyze.c</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>CSV 出力ループで mesh_set 地理範囲外ピークをスキップ（C 側フィルタ）</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="K2:K14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未対応,対応中,対応完了,解決済,却下"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1989,7 +2065,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1999,7 +2075,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2020,7 +2096,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2135,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2107,7 +2183,7 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2135,7 +2211,7 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2173,7 +2249,7 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -2197,7 +2273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2368,6 +2444,286 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B28" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -280,12 +280,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$31</f>
+              <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$31</f>
+              <f>'欠陥収束'!$B$2:$B$33</f>
             </numRef>
           </yVal>
         </ser>
@@ -314,12 +314,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$31</f>
+              <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$31</f>
+              <f>'欠陥収束'!$C$2:$C$33</f>
             </numRef>
           </yVal>
         </ser>
@@ -348,12 +348,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'欠陥収束'!$A$2:$A$31</f>
+              <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$31</f>
+              <f>'欠陥収束'!$D$2:$D$33</f>
             </numRef>
           </yVal>
         </ser>
@@ -364,7 +364,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46159"/>
+          <max val="46161"/>
           <min val="46130"/>
         </scaling>
         <axPos val="l"/>
@@ -929,7 +929,11 @@
           <t>scripts/merge.py</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>scripts/merge.py の expected_count() を修正: 代表レコードの center_mesh ではなく peak_lat/peak_lon からピークの属する 1 次メッシュコードを算出し、そのメッシュをどれだけの解析が含むかで expected_count を計算する</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>stability判定精度の問題。ピーク検出自体への影響はない。</t>
@@ -1009,7 +1013,11 @@
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>src/mesh_analyze.c の log_dir パス生成部分でファイル名を '&lt;meshcode&gt;.log' から 'findsummits_&lt;meshcode&gt;.log' に変更する（snprintf のフォーマット文字列を修正）</t>
+        </is>
+      </c>
       <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="inlineStr"/>
       <c r="R3" s="4" t="inlineStr"/>
@@ -1085,7 +1093,11 @@
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>src/mesh_analyze.c のログ出力部分に time() を使って解析開始時刻・終了時刻・所要時間（秒）を記録するコードを追加する。prefetch_tiles.py の実装を参考にする。BUG-002 と同じ箇所のため同一 PR での対応を推奨</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>BUG-002と同じ箇所（mesh_analyze.c）の修正なのでまとめて対応推奨。</t>
@@ -1165,7 +1177,11 @@
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>scripts/prefetch_tiles.py のログファイル名生成部分で datetime.utcnow() を datetime.now() に変更して JST ベースのファイル名にする。または UTC 使用のままとしてコメント・ドキュメントに UTC 前提である旨を明記する</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
@@ -1241,7 +1257,11 @@
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>段階的に調査・対応: ①TIMEOUT / LOW_SPEED_TIME の値を調整して改善確認 ②効果なければリトライロジック（失敗タイルをキューに積み再試行）を追加 ③それでも改善しない場合は残り N 枚を直列（1スレッド）フォールバックで処理する実装を検討</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
@@ -2273,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2724,6 +2744,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -124,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,7 +155,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -254,12 +251,15 @@
       </tx>
     </title>
     <plotArea>
-      <scatterChart>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>累計登録</v>
+            <strRef>
+              <f>'欠陥収束'!B1</f>
+            </strRef>
           </tx>
           <spPr>
             <a:ln w="20000">
@@ -270,30 +270,31 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
+            <symbol val="none"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
-          <xVal>
+          <cat>
             <numRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
-          </xVal>
-          <yVal>
+          </cat>
+          <val>
             <numRef>
               <f>'欠陥収束'!$B$2:$B$33</f>
             </numRef>
-          </yVal>
+          </val>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>対応累計</v>
+            <strRef>
+              <f>'欠陥収束'!C1</f>
+            </strRef>
           </tx>
           <spPr>
             <a:ln w="20000">
@@ -304,30 +305,31 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
+            <symbol val="none"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
-          <xVal>
+          <cat>
             <numRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
-          </xVal>
-          <yVal>
+          </cat>
+          <val>
             <numRef>
               <f>'欠陥収束'!$C$2:$C$33</f>
             </numRef>
-          </yVal>
+          </val>
         </ser>
         <ser>
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>確認累計</v>
+            <strRef>
+              <f>'欠陥収束'!D1</f>
+            </strRef>
           </tx>
           <spPr>
             <a:ln w="20000">
@@ -338,37 +340,33 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
+            <symbol val="none"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
-          <xVal>
+          <cat>
             <numRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
             </numRef>
-          </xVal>
-          <yVal>
+          </cat>
+          <val>
             <numRef>
               <f>'欠陥収束'!$D$2:$D$33</f>
             </numRef>
-          </yVal>
+          </val>
         </ser>
         <axId val="10"/>
-        <axId val="20"/>
-      </scatterChart>
-      <valAx>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46161"/>
-          <min val="46130"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -384,13 +382,13 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="YYYY-MM-DD" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="20"/>
-      </valAx>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
       <valAx>
-        <axId val="20"/>
+        <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
           <min val="0"/>
@@ -2325,8 +2323,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
-        <v>46130</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -2339,8 +2339,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
-        <v>46131</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -2353,8 +2355,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
-        <v>46132</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
@@ -2367,8 +2371,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>46133</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
@@ -2381,8 +2387,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>46134</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
@@ -2395,8 +2403,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>46135</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -2409,8 +2419,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>46136</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -2423,8 +2435,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>46137</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>6</v>
@@ -2437,8 +2451,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n">
-        <v>46138</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>12</v>
@@ -2451,8 +2467,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>46139</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2465,8 +2483,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>46140</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2479,8 +2499,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>46141</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
       </c>
       <c r="B13" t="n">
         <v>13</v>
@@ -2493,8 +2515,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>46142</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
       </c>
       <c r="B14" t="n">
         <v>13</v>
@@ -2507,8 +2531,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>46143</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
       </c>
       <c r="B15" t="n">
         <v>13</v>
@@ -2521,8 +2547,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>46144</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -2535,8 +2563,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
-        <v>46145</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -2549,8 +2579,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>46146</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -2563,8 +2595,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>46147</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -2577,8 +2611,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>46148</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -2591,8 +2627,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
-        <v>46149</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -2605,8 +2643,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>46150</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -2619,8 +2659,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
-        <v>46151</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -2633,8 +2675,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>46152</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2647,8 +2691,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
-        <v>46153</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2661,8 +2707,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>46154</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2675,8 +2723,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>46155</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -2689,8 +2739,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
-        <v>46156</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -2703,8 +2755,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>46157</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -2717,8 +2771,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>46158</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -2731,8 +2787,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>46159</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -2745,8 +2803,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>46160</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -2759,8 +2819,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
-        <v>46161</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
       </c>
       <c r="B33" t="n">
         <v>14</v>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -278,9 +278,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -313,9 +313,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -348,9 +348,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'欠陥収束'!$A$2:$A$33</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -279,12 +279,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$33</f>
+              <f>'欠陥収束'!$A$2:$A$50</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$33</f>
+              <f>'欠陥収束'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -314,12 +314,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$33</f>
+              <f>'欠陥収束'!$A$2:$A$50</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$33</f>
+              <f>'欠陥収束'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$33</f>
+              <f>'欠陥収束'!$A$2:$A$50</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$33</f>
+              <f>'欠陥収束'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -1961,43 +1961,43 @@
       <c r="R14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>BUG-014</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>combined 画像の地理境界外ピークが CSV に混入する</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>タイル座標のフロア演算により combined 画像の端タイルが地理的メッシュ境界より約17px外側へはみ出しており、そのはみ出し部分で検出されたピークが CSV に混入する。9メッシュ解析の検証で analysis_count=2/3 の異常ピーク34件として確認。</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -2007,34 +2007,38 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>対応完了</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>CSV 出力ループで mesh_set 地理範囲外ピークをスキップ（C 側フィルタ）</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2093,7 +2097,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2103,7 +2107,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2114,7 +2118,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2157,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2163,7 +2167,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2201,7 +2205,7 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2229,7 +2233,7 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2267,7 +2271,7 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2291,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2559,7 +2563,7 @@
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -2591,7 +2595,7 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2607,7 +2611,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2623,7 +2627,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2639,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2655,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -2671,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -2687,7 +2691,7 @@
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -2703,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -2719,7 +2723,7 @@
         <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2735,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -2751,7 +2755,7 @@
         <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2767,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -2783,7 +2787,7 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -2799,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -2815,7 +2819,7 @@
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -2831,7 +2835,279 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>14</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>14</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>14</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>14</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>14</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>14</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -279,14 +279,15 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$50</f>
+              <f>'欠陥収束'!$A$2:$A$73</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$50</f>
+              <f>'欠陥収束'!$B$2:$B$73</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
@@ -314,14 +315,15 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$50</f>
+              <f>'欠陥収束'!$A$2:$A$73</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$50</f>
+              <f>'欠陥収束'!$C$2:$C$73</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="2"/>
@@ -349,14 +351,15 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$50</f>
+              <f>'欠陥収束'!$A$2:$A$73</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$50</f>
+              <f>'欠陥収束'!$D$2:$D$73</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -2295,7 +2298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3110,6 +3113,374 @@
         <v>8</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>14</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>14</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>14</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>14</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>14</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>14</v>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>14</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>14</v>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>14</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>14</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>14</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>14</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>14</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>14</v>
+      </c>
+      <c r="C71" t="n">
+        <v>8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>14</v>
+      </c>
+      <c r="C72" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>14</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -279,12 +279,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$73</f>
+              <f>'欠陥収束'!$A$2:$A$76</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$73</f>
+              <f>'欠陥収束'!$B$2:$B$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -315,12 +315,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$73</f>
+              <f>'欠陥収束'!$A$2:$A$76</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$73</f>
+              <f>'欠陥収束'!$C$2:$C$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -351,12 +351,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$73</f>
+              <f>'欠陥収束'!$A$2:$A$76</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$73</f>
+              <f>'欠陥収束'!$D$2:$D$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2043,18 +2043,186 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>BUG-015</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>load_dotenv()がINI値の先頭空白をトリムせずDATA_DIR未設定環境でパスが壊れる</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>params/config.iniは「DATA_DIR = /data」(等号の後に半角スペース)と記述されている。load_dotenv()は値の先頭空白をトリムしない(末尾のみトリム)ため、環境変数DATA_DIRが未設定の環境で実行するとdata_dirが" /data"(先頭スペース付き)になり、以降構築される全パス(tile_dir/img_dir/result_dir)が壊れる。9メッシュ結合(5237-5439)でのtest_terrain_image実行時に、(a) elev_fill_nodata_dem10b()のtile_dem10b_is_cached()が実在する13683件を含む全15481件を「未キャッシュ」と誤判定、(b) save_terrain_rgb_image()のfopen()が存在しないパスへの書き込みを試み失敗(地形図PNG未生成)、として発覚。setenv(...,0)で既存の環境変数を優先するため、環境変数DATA_DIRが別途正しく設定されている運用環境では顕在化しない可能性がある。</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Sonnet</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>src/main.c,tests/test_mesh_analyze.c,tests/test_terrain_image.c</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>DATA_DIR環境変数が未設定の状態で実行すると毎回</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>src/main.c</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>load_dotenv()のvalパース処理(vstart = eq + 1の直後)に先頭空白/タブのスキップを追加する。main.c/test_mesh_analyze.c/test_terrain_image.cの3箇所に同一ロジックが重複実装されているため、修正は3箇所全てに適用する。</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>BUG-016</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>prefetch_tiles.pyの進捗表示がdem5フォールバック試行分を含み100%を超える</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>進捗表示(進捗: X/Y (Z%))の分子X(_total_done()の集計)はdem5フォールバック試行数(a→b→cで1ジョブが最大3回カウントされ得る)を含むが、分母Y(total_jobs)はジョブ数のまま。実測で9メッシュ(5237-5439)分の実行時に92899/77131(120.4%相当)まで進捗が到達し、表示上「進捗率」がユーザーに誤解を与える。実処理自体は正常完了しており(エラー0件)、機能的な欠陥ではなく表示のみの問題。</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Sonnet</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>prefetch</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>scripts/prefetch_tiles.py</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>dem5aが404となるタイルを多く含むメッシュリストで実行すると毎回</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>scripts/prefetch_tiles.py</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>進捗表示の分母を実際のフォールバック試行込みの総カウント数に変更する、または分子をジョブ完了数(job_queueのtask_done基準)に変更するなど、分子分母の基準を揃える。</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="K2:K15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未対応,対応中,対応完了,解決済,却下"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2090,7 +2258,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2110,7 +2278,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2121,7 +2289,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2338,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2298,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3481,6 +3649,54 @@
         <v>8</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>14</v>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -72,12 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBE0"/>
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
+        <fgColor rgb="00FFFBE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,10 +136,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1108,47 +1108,47 @@
       <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>prefetchログファイル名の時刻がUTC表記</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>ファイル名（例: prefetch_20260425_085043.log）は開始時刻のUTCから生成されているが、ls -lのmtimeはJST表示のため約9時間ずれて見える。ファイル名の時刻をJSTに統一するか、UTC前提ならドキュメント化が必要。</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>prefetch</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -1158,34 +1158,42 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py のログファイル名生成部分で datetime.utcnow() を datetime.now() に変更して JST ベースのファイル名にする。または UTC 使用のままとしてコメント・ドキュメントに UTC 前提である旨を明記する</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1233,7 +1241,7 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1268,47 +1276,47 @@
       <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>dem10bが存在しないタイルがある（GSI側未整備）</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>prefetchしても一部タイルが取得できない。GSI側がHTTP 404を返すため（取得漏れではない）。9メッシュ範囲で欠損4,581枚すべてを30件サンプリングして全件404を確認済み。欠損は南部メッシュ（35.7°N以南）に集中。Cコードが NODATA(-9999)扱いで解析続行するため動作上の問題なし。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>src/elevation.c / scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -1318,85 +1326,85 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>却下</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>GSI側の問題のため対応不可。Wontfix。</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>terrain PNGでの矩形ブロック状の異常はこれが原因（仕様として受容）。</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>BUG-007</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>load_mesh_tile() 前行ゼロリセットバグ（タイル上書き破壊）</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>load_mesh_tile() でタイル書き込み後に前行を 0 リセットしていた。calloc で初期化済みのためリセット不要だが、タイルデータを上書き破壊していた致命的バグ。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -1406,85 +1414,85 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>calloc 初期化済みのため、リセットコードを削除。</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>BUG-008</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>コル検出バグ（海面境界との接触を「コル」として誤検出）</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Union-Find の union() 時に peak_id &lt; 0（海面コンポーネント）のチェックが抜けていた。海面境界との接触を「コル」として誤検出し、山頂の比高が過小に計算されていた。</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>UT</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>src/unionfind.c</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -1494,85 +1502,85 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>src/unionfind.c</t>
         </is>
       </c>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>union 時に peak_id &lt; 0 チェックを追加して海面コンポーネントを除外。</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>BUG-009</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>整数オーバーフロー/SIGSEGV（5239解析で2.7億px &gt; int32_t上限）</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>ピクセルインデックスを int32_t で管理していたため、5239 解析（70,146×38,402px = 約2.7億px）で int32_t 上限（2.1億）を超えオーバーフロー → SIGSEGV で異常終了。</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>src/analyze.c, src/unionfind.h/c, src/elevation.c</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
@@ -1582,302 +1590,302 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>src/analyze.c</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>ピクセルインデックスを uint32_t / size_t に変更。コミット: fb9fcfd</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>BUG-010</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>dem10b URL誤設定（dem10b_png → dem_png）</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>prefetch_tiles.py の GSI_DEM10B_URL が dem10b_png だったが、正しいサービス名は dem_png。HTTP 404 が返り続けていたが取得漏れと区別できなかった。</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>prefetch</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>GSI_DEM10B_URL を dem_png に修正。動作確認済み（HTTP 200）。コミット: fb9fcfd</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>BUG-011</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>dem10b座標変換バグ（terrain PNG 格子状パターンの原因）</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>elev_fill_nodata_dem10b() と elev_load_with_overlap_8dir_with_dem10() の z15→z14 ピクセル変換で * TILE_PIX（256）を使っていた。dem10b は 256×256px なのに 512×512px として扱い、z14 タイルの右半分・下半分の NODATA が補完されず terrain PNG が格子状になっていた。</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>src/elevation.c</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>src/elevation.c</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>* TILE_PIX → * (TILE_PIX/2) + (px-1)/2 に修正。コミット: d0bb0b9</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>BUG-012</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>DEFAULT_SUMMITSLIST パス誤設定（DATA_DIR/ref/ → プロジェクト直下）</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>merge.py の DEFAULT_SUMMITSLIST が DATA_DIR 配下の ref/ を参照していた。DATA_DIR は環境依存パスのためプロジェクト同梱の summitslist.csv が見つからなかった。</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>merge.py</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>scripts/merge.py</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>JJ1XGO</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>scripts/merge.py</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>Path(__file__).parent.parent / 'ref/summitslist.csv' に修正。</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
@@ -1964,127 +1972,127 @@
       <c r="R14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>BUG-014</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>combined 画像の地理境界外ピークが CSV に混入する</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>タイル座標のフロア演算により combined 画像の端タイルが地理的メッシュ境界より約17px外側へはみ出しており、そのはみ出し部分で検出されたピークが CSV に混入する。9メッシュ解析の検証で analysis_count=2/3 の異常ピーク34件として確認。</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>解析エンジン</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>毎回</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>src/mesh_analyze.c</t>
         </is>
       </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>CSV 出力ループで mesh_set 地理範囲外ピークをスキップ（C 側フィルタ）</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>BUG-015</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>load_dotenv()がINI値の先頭空白をトリムせずDATA_DIR未設定環境でパスが壊れる</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>params/config.iniは「DATA_DIR = /data」(等号の後に半角スペース)と記述されている。load_dotenv()は値の先頭空白をトリムしない(末尾のみトリム)ため、環境変数DATA_DIRが未設定の環境で実行するとdata_dirが" /data"(先頭スペース付き)になり、以降構築される全パス(tile_dir/img_dir/result_dir)が壊れる。9メッシュ結合(5237-5439)でのtest_terrain_image実行時に、(a) elev_fill_nodata_dem10b()のtile_dem10b_is_cached()が実在する13683件を含む全15481件を「未キャッシュ」と誤判定、(b) save_terrain_rgb_image()のfopen()が存在しないパスへの書き込みを試み失敗(地形図PNG未生成)、として発覚。setenv(...,0)で既存の環境変数を優先するため、環境変数DATA_DIRが別途正しく設定されている運用環境では顕在化しない可能性がある。</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Sonnet</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>src/main.c,tests/test_mesh_analyze.c,tests/test_terrain_image.c</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>DATA_DIR環境変数が未設定の状態で実行すると毎回</t>
         </is>
@@ -2094,81 +2102,81 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>src/main.c</t>
         </is>
       </c>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>load_dotenv()のvalパース処理(vstart = eq + 1の直後)に先頭空白/タブのスキップを追加する。main.c/test_mesh_analyze.c/test_terrain_image.cの3箇所に同一ロジックが重複実装されているため、修正は3箇所全てに適用する。</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>BUG-016</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>prefetch_tiles.pyの進捗表示がdem5フォールバック試行分を含み100%を超える</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>進捗表示(進捗: X/Y (Z%))の分子X(_total_done()の集計)はdem5フォールバック試行数(a→b→cで1ジョブが最大3回カウントされ得る)を含むが、分母Y(total_jobs)はジョブ数のまま。実測で9メッシュ(5237-5439)分の実行時に92899/77131(120.4%相当)まで進捗が到達し、表示上「進捗率」がユーザーに誤解を与える。実処理自体は正常完了しており(エラー0件)、機能的な欠陥ではなく表示のみの問題。</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Sonnet</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>prefetch</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>dem5aが404となるタイルを多く含むメッシュリストで実行すると毎回</t>
         </is>
@@ -2178,34 +2186,34 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
       </c>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>scripts/prefetch_tiles.py</t>
         </is>
       </c>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>進捗表示の分母を実際のフォールバック試行込みの総カウント数に変更する、または分子をジョブ完了数(job_queueのtask_done基準)に変更するなど、分子分母の基準を揃える。</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
@@ -2268,7 +2276,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2286,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2289,7 +2297,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2316,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2338,7 +2346,7 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -2386,7 +2394,7 @@
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2424,7 +2432,7 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2442,7 +2450,7 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3691,10 +3699,10 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/mgmt/tracker/reports/bugs_export.xlsx
+++ b/mgmt/tracker/reports/bugs_export.xlsx
@@ -279,12 +279,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$76</f>
+              <f>'欠陥収束'!$A$2:$A$78</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$B$2:$B$76</f>
+              <f>'欠陥収束'!$B$2:$B$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -315,12 +315,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$76</f>
+              <f>'欠陥収束'!$A$2:$A$78</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$C$2:$C$76</f>
+              <f>'欠陥収束'!$C$2:$C$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -351,12 +351,12 @@
           </marker>
           <cat>
             <strRef>
-              <f>'欠陥収束'!$A$2:$A$76</f>
+              <f>'欠陥収束'!$A$2:$A$78</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'欠陥収束'!$D$2:$D$76</f>
+              <f>'欠陥収束'!$D$2:$D$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2219,18 +2219,98 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BUG-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>docs-date-check hook がコードフェンス内の最終更新日プレースホルダに誤検知する</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>docs/CLAUDE.md はヘッダーテーブルを持たないが、フォーマット標準のコードフェンス内テンプレート（| 最終更新日 | YYYY-MM-DD |）が grep に一致し、編集のたびに当日付への更新を誤要求する。テンプレートを日付に書き換えると仕様例示が壊れるため従えない指示になる</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Fable 5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>.claude/hooks/docs-date-check.sh</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>毎回</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>対応完了</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>.claude/hooks/docs-date-check.sh</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>実ヘッダーを持たない docs/CLAUDE.md を検査対象から除外する（case 節で早期 exit）</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="K2:K17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未対応,対応中,対応完了,解決済,却下"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"URD,SRS,HLD,LLD,COD,UT,IT,ST,OPS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2244,7 +2324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2266,7 +2346,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2276,7 +2356,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2297,7 +2377,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2416,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2394,7 +2474,7 @@
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2435,31 +2515,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>発生源ステージ別（未解決）</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="B25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B27" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2474,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3705,6 +3805,38 @@
         <v>11</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>11</v>
+      </c>
+      <c r="D77" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
